--- a/artfynd/A 2916-2025 artfynd.xlsx
+++ b/artfynd/A 2916-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126080902</v>
       </c>
       <c r="B2" t="n">
-        <v>98280</v>
+        <v>98281</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>126081082</v>
       </c>
       <c r="B3" t="n">
-        <v>98375</v>
+        <v>98376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2916-2025 artfynd.xlsx
+++ b/artfynd/A 2916-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126080902</v>
       </c>
       <c r="B2" t="n">
-        <v>98281</v>
+        <v>98283</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>126081082</v>
       </c>
       <c r="B3" t="n">
-        <v>98376</v>
+        <v>98378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2916-2025 artfynd.xlsx
+++ b/artfynd/A 2916-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126080902</v>
       </c>
       <c r="B2" t="n">
-        <v>98283</v>
+        <v>98285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>126081082</v>
       </c>
       <c r="B3" t="n">
-        <v>98378</v>
+        <v>98380</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2916-2025 artfynd.xlsx
+++ b/artfynd/A 2916-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126080902</v>
       </c>
       <c r="B2" t="n">
-        <v>98285</v>
+        <v>98287</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>126081082</v>
       </c>
       <c r="B3" t="n">
-        <v>98380</v>
+        <v>98382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2916-2025 artfynd.xlsx
+++ b/artfynd/A 2916-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126080902</v>
       </c>
       <c r="B2" t="n">
-        <v>98287</v>
+        <v>98291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>126081082</v>
       </c>
       <c r="B3" t="n">
-        <v>98382</v>
+        <v>98386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2916-2025 artfynd.xlsx
+++ b/artfynd/A 2916-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126080902</v>
       </c>
       <c r="B2" t="n">
-        <v>98291</v>
+        <v>98294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>126081082</v>
       </c>
       <c r="B3" t="n">
-        <v>98386</v>
+        <v>98389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2916-2025 artfynd.xlsx
+++ b/artfynd/A 2916-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126080902</v>
       </c>
       <c r="B2" t="n">
-        <v>98294</v>
+        <v>98303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>126081082</v>
       </c>
       <c r="B3" t="n">
-        <v>98389</v>
+        <v>98398</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
